--- a/qualitative analysis results (version 1).xlsx
+++ b/qualitative analysis results (version 1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fredr\kod\exjobb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{ADC4C15C-7727-40A2-A2E2-812138161E04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09DF69E5-281B-46AE-8FD1-A5DB8DFF0F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="49">
   <si>
     <t>File</t>
   </si>
@@ -172,6 +171,18 @@
   </si>
   <si>
     <t>I kronor:</t>
+  </si>
+  <si>
+    <t>total latency for 100 runs:</t>
+  </si>
+  <si>
+    <t>57.0141278999763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">average per file: </t>
+  </si>
+  <si>
+    <t>0.570141278999763</t>
   </si>
 </sst>
 </file>
@@ -2133,19 +2144,19 @@
         <v>283</v>
       </c>
       <c r="H21">
-        <f>SUM(B21,D21,F21)</f>
+        <f t="shared" ref="H21:I23" si="0">SUM(B21,D21,F21)</f>
         <v>1803.43</v>
       </c>
       <c r="I21">
-        <f>SUM(C21,E21,G21)</f>
+        <f t="shared" si="0"/>
         <v>566</v>
       </c>
       <c r="J21">
-        <f>SUM(D21,F21)</f>
+        <f t="shared" ref="J21:K23" si="1">SUM(D21,F21)</f>
         <v>1536.19</v>
       </c>
       <c r="K21">
-        <f>SUM(E21,G21)</f>
+        <f t="shared" si="1"/>
         <v>423</v>
       </c>
     </row>
@@ -2172,19 +2183,19 @@
         <v>9274</v>
       </c>
       <c r="H22">
-        <f>SUM(B22,D22,F22)</f>
+        <f t="shared" si="0"/>
         <v>1821.45</v>
       </c>
       <c r="I22">
-        <f>SUM(C22,E22,G22)</f>
+        <f t="shared" si="0"/>
         <v>16108</v>
       </c>
       <c r="J22">
-        <f>SUM(D22,F22)</f>
+        <f t="shared" si="1"/>
         <v>1547.7800000000002</v>
       </c>
       <c r="K22">
-        <f>SUM(E22,G22)</f>
+        <f t="shared" si="1"/>
         <v>13159</v>
       </c>
     </row>
@@ -2211,19 +2222,19 @@
         <v>2770</v>
       </c>
       <c r="H23">
-        <f>SUM(B23,D23,F23)</f>
+        <f t="shared" si="0"/>
         <v>5612.18</v>
       </c>
       <c r="I23">
-        <f>SUM(C23,E23,G23)</f>
+        <f t="shared" si="0"/>
         <v>4957</v>
       </c>
       <c r="J23">
-        <f>SUM(D23,F23)</f>
+        <f t="shared" si="1"/>
         <v>4723.2</v>
       </c>
       <c r="K23">
-        <f>SUM(E23,G23)</f>
+        <f t="shared" si="1"/>
         <v>4126</v>
       </c>
     </row>
@@ -2308,7 +2319,7 @@
         <v>57.215200000000003</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B44" t="s">
         <v>40</v>
       </c>
@@ -2319,7 +2330,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>2</v>
       </c>
@@ -2333,7 +2344,7 @@
         <v>1040.3900000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>3</v>
       </c>
@@ -2346,8 +2357,14 @@
       <c r="D46">
         <v>1058.3800000000001</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="F46" t="s">
+        <v>45</v>
+      </c>
+      <c r="G46" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>1</v>
       </c>
@@ -2359,6 +2376,12 @@
       </c>
       <c r="D47">
         <v>3183.9</v>
+      </c>
+      <c r="F47" t="s">
+        <v>47</v>
+      </c>
+      <c r="G47" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
